--- a/fixtures/manual-check/data.xlsx
+++ b/fixtures/manual-check/data.xlsx
@@ -7,14 +7,52 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Pivot" sheetId="2" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="0" r:id="rId7"/>
+  </x:pivotCaches>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Region</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Product</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quarter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sales</x:t>
+  </x:si>
+  <x:si>
+    <x:t>East</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>West</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -72,7 +110,217 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
+  <x:dxfs count="1">
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor auto="1"/>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>Sales by region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1'!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1'!$A$11:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1'!$B$11:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>530</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="100001"/>
+        <c:axId val="100002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="100001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="100002"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="100001"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R772162dd02474d4b"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1524000" cy="857250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1524000" cy="857250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="SalesPivot" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+  <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
+  <pivotFields count="4">
+    <pivotField name="Region" axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField name="Quarter" axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -366,30 +614,242 @@
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0">
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B1" s="0">
-        <x:f>_xlfn.SEQUENCE(3)</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2">
-      <x:c r="A2" s="0">
+      <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0">
-        <x:f>SUM(A1:A2)</x:f>
+      <x:c r="D1" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>370</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>530</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="D2:D7">
+    <x:cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <x:formula>150</x:formula>
+    </x:cfRule>
+    <x:cfRule type="colorScale" priority="2">
+      <x:colorScale>
+        <x:cfvo type="min"/>
+        <x:cfvo type="max"/>
+        <x:color rgb="FFFFFFFF"/>
+        <x:color rgb="FF63BE7B"/>
+      </x:colorScale>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:drawing r:id="Re14416f3714941b8"/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
+  <x:cacheSource type="worksheet">
+    <x:worksheetSource ref="A1:D7" sheet="Sheet1"/>
+  </x:cacheSource>
+  <x:cacheFields>
+    <x:cacheField name="Region">
+      <x:sharedItems count="2">
+        <x:s v="East"/>
+        <x:s v="West"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Product">
+      <x:sharedItems count="2">
+        <x:s v="Apple"/>
+        <x:s v="Pear"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Quarter">
+      <x:sharedItems count="2">
+        <x:s v="Q1"/>
+        <x:s v="Q2"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Sales">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80" maxValue="250" count="6">
+        <x:n v="100"/>
+        <x:n v="150"/>
+        <x:n v="200"/>
+        <x:n v="250"/>
+        <x:n v="120"/>
+        <x:n v="80"/>
+      </x:sharedItems>
+    </x:cacheField>
+  </x:cacheFields>
+</x:pivotCacheDefinition>
+</file>
+
+<file path=pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
+  <r>
+    <s v="East"/>
+    <s v="Apple"/>
+    <s v="Q1"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <s v="East"/>
+    <s v="Pear"/>
+    <s v="Q2"/>
+    <n v="150"/>
+  </r>
+  <r>
+    <s v="West"/>
+    <s v="Apple"/>
+    <s v="Q1"/>
+    <n v="200"/>
+  </r>
+  <r>
+    <s v="West"/>
+    <s v="Pear"/>
+    <s v="Q2"/>
+    <n v="250"/>
+  </r>
+  <r>
+    <s v="East"/>
+    <s v="Apple"/>
+    <s v="Q2"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <s v="West"/>
+    <s v="Pear"/>
+    <s v="Q1"/>
+    <n v="80"/>
+  </r>
+</pivotCacheRecords>
 </file>